--- a/data/batches/B18_Mixed/Test_Validation_Report/Test_Validation_Report_B18.xlsx
+++ b/data/batches/B18_Mixed/Test_Validation_Report/Test_Validation_Report_B18.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -13303,11 +13303,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13319,16 +13315,8 @@
       <c r="H144" t="n">
         <v>78</v>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13336,7 +13324,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13346,22 +13334,22 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13386,11 +13374,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13402,16 +13386,8 @@
       <c r="H145" t="n">
         <v>81</v>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13419,7 +13395,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13429,22 +13405,22 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13469,11 +13445,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13485,16 +13457,8 @@
       <c r="H146" t="n">
         <v>192</v>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13502,7 +13466,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13512,22 +13476,22 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13552,11 +13516,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13568,16 +13528,8 @@
       <c r="H147" t="n">
         <v>276</v>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13585,7 +13537,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13595,22 +13547,22 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13635,11 +13587,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13651,16 +13599,8 @@
       <c r="H148" t="n">
         <v>83</v>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13668,7 +13608,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13678,22 +13618,22 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13718,11 +13658,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE02-0014</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13734,16 +13670,8 @@
       <c r="H149" t="n">
         <v>164</v>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13751,7 +13679,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13761,22 +13689,22 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13801,11 +13729,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13817,16 +13741,8 @@
       <c r="H150" t="n">
         <v>96</v>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13834,7 +13750,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13844,22 +13760,22 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13884,11 +13800,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13900,16 +13812,8 @@
       <c r="H151" t="n">
         <v>263</v>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -13917,7 +13821,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13927,22 +13831,22 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -13967,11 +13871,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -13983,16 +13883,8 @@
       <c r="H152" t="n">
         <v>126</v>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14000,7 +13892,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14010,22 +13902,22 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14050,11 +13942,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0005</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -14066,16 +13954,8 @@
       <c r="H153" t="n">
         <v>270</v>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14083,7 +13963,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14093,22 +13973,22 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14133,11 +14013,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>BI-1245.110-BRA_SITE01-0010</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -14149,16 +14025,8 @@
       <c r="H154" t="n">
         <v>38</v>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14166,7 +14034,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14176,22 +14044,22 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14216,11 +14084,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0008</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -14232,16 +14096,8 @@
       <c r="H155" t="n">
         <v>85</v>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14249,7 +14105,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14259,22 +14115,22 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14299,11 +14155,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>BI-1245.110-RUS_SITE01-0011</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -14315,16 +14167,8 @@
       <c r="H156" t="n">
         <v>244</v>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14332,7 +14176,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14342,22 +14186,22 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14382,11 +14226,7 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>BI-1245.110-RUS_SITE01-0011</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>CMSTTPT</t>
@@ -14398,16 +14238,8 @@
       <c r="H157" t="n">
         <v>239</v>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14415,7 +14247,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14425,22 +14257,22 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14465,11 +14297,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14481,16 +14309,8 @@
       <c r="H158" t="n">
         <v>2328</v>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14498,7 +14318,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14508,22 +14328,22 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14548,11 +14368,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14564,16 +14380,8 @@
       <c r="H159" t="n">
         <v>2040</v>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14581,7 +14389,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14591,22 +14399,22 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14631,11 +14439,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14647,16 +14451,8 @@
       <c r="H160" t="n">
         <v>2057</v>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14664,7 +14460,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14674,22 +14470,22 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14714,11 +14510,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14730,16 +14522,8 @@
       <c r="H161" t="n">
         <v>5277</v>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14747,7 +14531,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14757,22 +14541,22 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14797,11 +14581,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14813,16 +14593,8 @@
       <c r="H162" t="n">
         <v>2109</v>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14830,7 +14602,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14840,22 +14612,22 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14880,11 +14652,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14896,16 +14664,8 @@
       <c r="H163" t="n">
         <v>4688</v>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14913,7 +14673,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14923,22 +14683,22 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -14963,11 +14723,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0016</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -14979,16 +14735,8 @@
       <c r="H164" t="n">
         <v>4865</v>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -14996,7 +14744,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -15006,22 +14754,22 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15046,11 +14794,7 @@
           <t>EC</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>BI-1245.110-CAN_SITE01-0015</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>ECSTTPT</t>
@@ -15062,16 +14806,8 @@
       <c r="H165" t="n">
         <v>2022</v>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15079,7 +14815,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -15089,22 +14825,22 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15129,11 +14865,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>BI-1245.110-KOR_SITE01-0012</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>AESTTPT</t>
@@ -15145,16 +14877,8 @@
       <c r="H166" t="n">
         <v>362</v>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15162,7 +14886,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -15172,22 +14896,22 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15212,11 +14936,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>AESTTPT</t>
@@ -15228,16 +14948,8 @@
       <c r="H167" t="n">
         <v>248</v>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15245,7 +14957,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -15255,22 +14967,22 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15295,11 +15007,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>AESTTPT</t>
@@ -15311,16 +15019,8 @@
       <c r="H168" t="n">
         <v>576</v>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15328,7 +15028,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -15338,22 +15038,22 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15378,11 +15078,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>AESTTPT</t>
@@ -15394,16 +15090,8 @@
       <c r="H169" t="n">
         <v>277</v>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15411,7 +15099,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -15421,22 +15109,22 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15461,11 +15149,7 @@
           <t>DV</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>DVSTTPT</t>
@@ -15477,16 +15161,8 @@
       <c r="H170" t="n">
         <v>233</v>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15494,7 +15170,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -15504,22 +15180,22 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15544,11 +15220,7 @@
           <t>DV</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>DVSTTPT</t>
@@ -15560,16 +15232,8 @@
       <c r="H171" t="n">
         <v>246</v>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15577,7 +15241,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15587,22 +15251,22 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15627,11 +15291,7 @@
           <t>DV</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>BI-1245.110-JPN_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>DVSTTPT</t>
@@ -15643,16 +15303,8 @@
       <c r="H172" t="n">
         <v>234</v>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15660,7 +15312,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15670,22 +15322,22 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -15710,11 +15362,7 @@
           <t>MH</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>MHSTTPT</t>
@@ -15726,16 +15374,8 @@
       <c r="H173" t="n">
         <v>71</v>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>BASELINE</t>
@@ -15743,7 +15383,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>SCREENING</t>
+          <t>BASELINE</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15753,22 +15393,22 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>New column injection mismatch</t>
+          <t>Duplicate with mutation verified successfully</t>
         </is>
       </c>
     </row>
@@ -17790,7 +17430,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -17841,7 +17481,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -18069,10 +17709,10 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -18087,7 +17727,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
     </row>
   </sheetData>
